--- a/artfynd/A 27666-2026 artfynd.xlsx
+++ b/artfynd/A 27666-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AY133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4523,32 +4523,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135265226</v>
+        <v>135265182</v>
       </c>
       <c r="B38" t="n">
-        <v>92318</v>
+        <v>96037</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2062</v>
+        <v>2387</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558706</v>
+        <v>558434</v>
       </c>
       <c r="R38" t="n">
-        <v>7089489</v>
+        <v>7089599</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4630,10 +4630,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135265182</v>
+        <v>135265176</v>
       </c>
       <c r="B39" t="n">
-        <v>96037</v>
+        <v>91937</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,21 +4641,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2387</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558434</v>
+        <v>558447</v>
       </c>
       <c r="R39" t="n">
-        <v>7089599</v>
+        <v>7089688</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4737,7 +4737,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135265176</v>
+        <v>135265184</v>
       </c>
       <c r="B40" t="n">
         <v>91937</v>
@@ -4775,7 +4775,7 @@
         <v>558447</v>
       </c>
       <c r="R40" t="n">
-        <v>7089688</v>
+        <v>7089602</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4844,7 +4844,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135265184</v>
+        <v>135265201</v>
       </c>
       <c r="B41" t="n">
         <v>91937</v>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558447</v>
+        <v>558585</v>
       </c>
       <c r="R41" t="n">
-        <v>7089602</v>
+        <v>7089565</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4951,7 +4951,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135265201</v>
+        <v>135265205</v>
       </c>
       <c r="B42" t="n">
         <v>91937</v>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558585</v>
+        <v>558587</v>
       </c>
       <c r="R42" t="n">
-        <v>7089565</v>
+        <v>7089597</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5058,7 +5058,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135265205</v>
+        <v>135265213</v>
       </c>
       <c r="B43" t="n">
         <v>91937</v>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558587</v>
+        <v>558649</v>
       </c>
       <c r="R43" t="n">
-        <v>7089597</v>
+        <v>7089561</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5165,7 +5165,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135265213</v>
+        <v>135265223</v>
       </c>
       <c r="B44" t="n">
         <v>91937</v>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558649</v>
+        <v>558688</v>
       </c>
       <c r="R44" t="n">
-        <v>7089561</v>
+        <v>7089529</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5272,7 +5272,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135265223</v>
+        <v>135265230</v>
       </c>
       <c r="B45" t="n">
         <v>91937</v>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558688</v>
+        <v>558661</v>
       </c>
       <c r="R45" t="n">
-        <v>7089529</v>
+        <v>7089487</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5379,7 +5379,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135265230</v>
+        <v>135265251</v>
       </c>
       <c r="B46" t="n">
         <v>91937</v>
@@ -5414,13 +5414,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558661</v>
+        <v>558939</v>
       </c>
       <c r="R46" t="n">
-        <v>7089487</v>
+        <v>7089407</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5486,7 +5486,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135265251</v>
+        <v>135265269</v>
       </c>
       <c r="B47" t="n">
         <v>91937</v>
@@ -5521,13 +5521,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558939</v>
+        <v>558693</v>
       </c>
       <c r="R47" t="n">
-        <v>7089407</v>
+        <v>7089579</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5593,7 +5593,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135265269</v>
+        <v>135265276</v>
       </c>
       <c r="B48" t="n">
         <v>91937</v>
@@ -5628,10 +5628,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558693</v>
+        <v>558441</v>
       </c>
       <c r="R48" t="n">
-        <v>7089579</v>
+        <v>7089856</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5700,7 +5700,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135265276</v>
+        <v>135265282</v>
       </c>
       <c r="B49" t="n">
         <v>91937</v>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558441</v>
+        <v>558404</v>
       </c>
       <c r="R49" t="n">
-        <v>7089856</v>
+        <v>7089923</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5807,32 +5807,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135265282</v>
+        <v>135265178</v>
       </c>
       <c r="B50" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558404</v>
+        <v>558421</v>
       </c>
       <c r="R50" t="n">
-        <v>7089923</v>
+        <v>7089676</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5914,7 +5914,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135265178</v>
+        <v>135265180</v>
       </c>
       <c r="B51" t="n">
         <v>79373</v>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558421</v>
+        <v>558437</v>
       </c>
       <c r="R51" t="n">
-        <v>7089676</v>
+        <v>7089672</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6021,7 +6021,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135265180</v>
+        <v>135265186</v>
       </c>
       <c r="B52" t="n">
         <v>79373</v>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558437</v>
+        <v>558467</v>
       </c>
       <c r="R52" t="n">
-        <v>7089672</v>
+        <v>7089616</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6128,7 +6128,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135265186</v>
+        <v>135265187</v>
       </c>
       <c r="B53" t="n">
         <v>79373</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558467</v>
+        <v>558506</v>
       </c>
       <c r="R53" t="n">
-        <v>7089616</v>
+        <v>7089686</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6235,7 +6235,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135265187</v>
+        <v>135265188</v>
       </c>
       <c r="B54" t="n">
         <v>79373</v>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558506</v>
+        <v>558521</v>
       </c>
       <c r="R54" t="n">
-        <v>7089686</v>
+        <v>7089662</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6342,7 +6342,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135265188</v>
+        <v>135265189</v>
       </c>
       <c r="B55" t="n">
         <v>79373</v>
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558521</v>
+        <v>558526</v>
       </c>
       <c r="R55" t="n">
-        <v>7089662</v>
+        <v>7089654</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6449,7 +6449,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135265189</v>
+        <v>135265193</v>
       </c>
       <c r="B56" t="n">
         <v>79373</v>
@@ -6484,10 +6484,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558526</v>
+        <v>558475</v>
       </c>
       <c r="R56" t="n">
-        <v>7089654</v>
+        <v>7089582</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6556,7 +6556,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135265193</v>
+        <v>135265212</v>
       </c>
       <c r="B57" t="n">
         <v>79373</v>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558475</v>
+        <v>558625</v>
       </c>
       <c r="R57" t="n">
-        <v>7089582</v>
+        <v>7089586</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6663,7 +6663,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135265212</v>
+        <v>135265214</v>
       </c>
       <c r="B58" t="n">
         <v>79373</v>
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558625</v>
+        <v>558645</v>
       </c>
       <c r="R58" t="n">
-        <v>7089586</v>
+        <v>7089563</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6770,7 +6770,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135265214</v>
+        <v>135265215</v>
       </c>
       <c r="B59" t="n">
         <v>79373</v>
@@ -6805,10 +6805,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558645</v>
+        <v>558634</v>
       </c>
       <c r="R59" t="n">
-        <v>7089563</v>
+        <v>7089551</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6877,7 +6877,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135265215</v>
+        <v>135265221</v>
       </c>
       <c r="B60" t="n">
         <v>79373</v>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558634</v>
+        <v>558674</v>
       </c>
       <c r="R60" t="n">
-        <v>7089551</v>
+        <v>7089534</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6984,7 +6984,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135265221</v>
+        <v>135265224</v>
       </c>
       <c r="B61" t="n">
         <v>79373</v>
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558674</v>
+        <v>558700</v>
       </c>
       <c r="R61" t="n">
-        <v>7089534</v>
+        <v>7089502</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7091,7 +7091,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135265224</v>
+        <v>135265239</v>
       </c>
       <c r="B62" t="n">
         <v>79373</v>
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558700</v>
+        <v>558742</v>
       </c>
       <c r="R62" t="n">
-        <v>7089502</v>
+        <v>7089364</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7198,7 +7198,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135265239</v>
+        <v>135265241</v>
       </c>
       <c r="B63" t="n">
         <v>79373</v>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558742</v>
+        <v>558749</v>
       </c>
       <c r="R63" t="n">
-        <v>7089364</v>
+        <v>7089324</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7305,7 +7305,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135265241</v>
+        <v>135265242</v>
       </c>
       <c r="B64" t="n">
         <v>79373</v>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558749</v>
+        <v>558780</v>
       </c>
       <c r="R64" t="n">
-        <v>7089324</v>
+        <v>7089379</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7412,7 +7412,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135265242</v>
+        <v>135265247</v>
       </c>
       <c r="B65" t="n">
         <v>79373</v>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558780</v>
+        <v>558830</v>
       </c>
       <c r="R65" t="n">
-        <v>7089379</v>
+        <v>7089398</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7519,7 +7519,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135265247</v>
+        <v>135265248</v>
       </c>
       <c r="B66" t="n">
         <v>79373</v>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558830</v>
+        <v>558860</v>
       </c>
       <c r="R66" t="n">
-        <v>7089398</v>
+        <v>7089394</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7626,7 +7626,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135265248</v>
+        <v>135265250</v>
       </c>
       <c r="B67" t="n">
         <v>79373</v>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558860</v>
+        <v>558931</v>
       </c>
       <c r="R67" t="n">
-        <v>7089394</v>
+        <v>7089393</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7733,7 +7733,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135265250</v>
+        <v>135265253</v>
       </c>
       <c r="B68" t="n">
         <v>79373</v>
@@ -7768,10 +7768,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558931</v>
+        <v>558922</v>
       </c>
       <c r="R68" t="n">
-        <v>7089393</v>
+        <v>7089432</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7840,7 +7840,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135265253</v>
+        <v>135265256</v>
       </c>
       <c r="B69" t="n">
         <v>79373</v>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558922</v>
+        <v>558847</v>
       </c>
       <c r="R69" t="n">
-        <v>7089432</v>
+        <v>7089436</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7947,7 +7947,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135265256</v>
+        <v>135265258</v>
       </c>
       <c r="B70" t="n">
         <v>79373</v>
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558847</v>
+        <v>558766</v>
       </c>
       <c r="R70" t="n">
-        <v>7089436</v>
+        <v>7089458</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8054,7 +8054,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135265258</v>
+        <v>135265259</v>
       </c>
       <c r="B71" t="n">
         <v>79373</v>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558766</v>
+        <v>558807</v>
       </c>
       <c r="R71" t="n">
-        <v>7089458</v>
+        <v>7089488</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8161,7 +8161,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135265259</v>
+        <v>135265260</v>
       </c>
       <c r="B72" t="n">
         <v>79373</v>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558807</v>
+        <v>558815</v>
       </c>
       <c r="R72" t="n">
-        <v>7089488</v>
+        <v>7089517</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8268,7 +8268,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135265260</v>
+        <v>135265264</v>
       </c>
       <c r="B73" t="n">
         <v>79373</v>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558815</v>
+        <v>558762</v>
       </c>
       <c r="R73" t="n">
-        <v>7089517</v>
+        <v>7089560</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8375,7 +8375,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135265264</v>
+        <v>135265265</v>
       </c>
       <c r="B74" t="n">
         <v>79373</v>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558762</v>
+        <v>558748</v>
       </c>
       <c r="R74" t="n">
-        <v>7089560</v>
+        <v>7089555</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8482,7 +8482,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135265265</v>
+        <v>135265266</v>
       </c>
       <c r="B75" t="n">
         <v>79373</v>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558748</v>
+        <v>558709</v>
       </c>
       <c r="R75" t="n">
-        <v>7089555</v>
+        <v>7089558</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8589,7 +8589,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135265266</v>
+        <v>135265270</v>
       </c>
       <c r="B76" t="n">
         <v>79373</v>
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558709</v>
+        <v>558594</v>
       </c>
       <c r="R76" t="n">
-        <v>7089558</v>
+        <v>7089645</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8696,7 +8696,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135265270</v>
+        <v>135265271</v>
       </c>
       <c r="B77" t="n">
         <v>79373</v>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>558594</v>
+        <v>558411</v>
       </c>
       <c r="R77" t="n">
-        <v>7089645</v>
+        <v>7089787</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8803,7 +8803,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135265271</v>
+        <v>135265274</v>
       </c>
       <c r="B78" t="n">
         <v>79373</v>
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>558411</v>
+        <v>558433</v>
       </c>
       <c r="R78" t="n">
-        <v>7089787</v>
+        <v>7089846</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8910,7 +8910,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135265274</v>
+        <v>135265279</v>
       </c>
       <c r="B79" t="n">
         <v>79373</v>
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558433</v>
+        <v>558443</v>
       </c>
       <c r="R79" t="n">
-        <v>7089846</v>
+        <v>7089881</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9017,7 +9017,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135265279</v>
+        <v>135265281</v>
       </c>
       <c r="B80" t="n">
         <v>79373</v>
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558443</v>
+        <v>558416</v>
       </c>
       <c r="R80" t="n">
-        <v>7089881</v>
+        <v>7089907</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9124,7 +9124,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135265281</v>
+        <v>135265286</v>
       </c>
       <c r="B81" t="n">
         <v>79373</v>
@@ -9159,10 +9159,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>558416</v>
+        <v>558437</v>
       </c>
       <c r="R81" t="n">
-        <v>7089907</v>
+        <v>7089960</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9231,7 +9231,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135265286</v>
+        <v>135265288</v>
       </c>
       <c r="B82" t="n">
         <v>79373</v>
@@ -9266,10 +9266,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>558437</v>
+        <v>558466</v>
       </c>
       <c r="R82" t="n">
-        <v>7089960</v>
+        <v>7089936</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9338,7 +9338,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135265288</v>
+        <v>135265292</v>
       </c>
       <c r="B83" t="n">
         <v>79373</v>
@@ -9373,13 +9373,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>558466</v>
+        <v>558483</v>
       </c>
       <c r="R83" t="n">
-        <v>7089936</v>
+        <v>7089932</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9445,7 +9445,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135265292</v>
+        <v>135265293</v>
       </c>
       <c r="B84" t="n">
         <v>79373</v>
@@ -9480,13 +9480,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>558483</v>
+        <v>558498</v>
       </c>
       <c r="R84" t="n">
-        <v>7089932</v>
+        <v>7089914</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9552,7 +9552,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135265293</v>
+        <v>135265303</v>
       </c>
       <c r="B85" t="n">
         <v>79373</v>
@@ -9587,10 +9587,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>558498</v>
+        <v>558479</v>
       </c>
       <c r="R85" t="n">
-        <v>7089914</v>
+        <v>7089873</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9659,7 +9659,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135265303</v>
+        <v>135265306</v>
       </c>
       <c r="B86" t="n">
         <v>79373</v>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>558479</v>
+        <v>558471</v>
       </c>
       <c r="R86" t="n">
-        <v>7089873</v>
+        <v>7089914</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9766,7 +9766,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135265306</v>
+        <v>135265311</v>
       </c>
       <c r="B87" t="n">
         <v>79373</v>
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>558471</v>
+        <v>558488</v>
       </c>
       <c r="R87" t="n">
-        <v>7089914</v>
+        <v>7089857</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9873,7 +9873,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135265311</v>
+        <v>135265315</v>
       </c>
       <c r="B88" t="n">
         <v>79373</v>
@@ -9908,10 +9908,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>558488</v>
+        <v>558497</v>
       </c>
       <c r="R88" t="n">
-        <v>7089857</v>
+        <v>7089769</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9980,7 +9980,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135265315</v>
+        <v>135265316</v>
       </c>
       <c r="B89" t="n">
         <v>79373</v>
@@ -10015,10 +10015,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>558497</v>
+        <v>558488</v>
       </c>
       <c r="R89" t="n">
-        <v>7089769</v>
+        <v>7089765</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10087,7 +10087,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135265316</v>
+        <v>135265317</v>
       </c>
       <c r="B90" t="n">
         <v>79373</v>
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>558488</v>
+        <v>558471</v>
       </c>
       <c r="R90" t="n">
-        <v>7089765</v>
+        <v>7089758</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10194,32 +10194,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135265317</v>
+        <v>97362210</v>
       </c>
       <c r="B91" t="n">
-        <v>79373</v>
+        <v>83307</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10229,13 +10229,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>558471</v>
+        <v>558451</v>
       </c>
       <c r="R91" t="n">
-        <v>7089758</v>
+        <v>7089974</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10259,22 +10259,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>18:02</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>18:02</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10289,22 +10279,26 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>97362210</v>
+        <v>135265262</v>
       </c>
       <c r="B92" t="n">
-        <v>83307</v>
+        <v>80488</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10312,21 +10306,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10336,13 +10330,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>558451</v>
+        <v>558806</v>
       </c>
       <c r="R92" t="n">
-        <v>7089974</v>
+        <v>7089561</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10366,12 +10360,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10386,48 +10390,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135265262</v>
+        <v>135265287</v>
       </c>
       <c r="B93" t="n">
-        <v>80488</v>
+        <v>5181</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>100526</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10437,10 +10437,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>558806</v>
+        <v>558439</v>
       </c>
       <c r="R93" t="n">
-        <v>7089561</v>
+        <v>7089960</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10509,7 +10509,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135265287</v>
+        <v>135265312</v>
       </c>
       <c r="B94" t="n">
         <v>5181</v>
@@ -10544,10 +10544,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>558439</v>
+        <v>558491</v>
       </c>
       <c r="R94" t="n">
-        <v>7089960</v>
+        <v>7089850</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10616,10 +10616,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135265312</v>
+        <v>135265272</v>
       </c>
       <c r="B95" t="n">
-        <v>5181</v>
+        <v>5201</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10627,21 +10627,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10651,10 +10651,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>558491</v>
+        <v>558413</v>
       </c>
       <c r="R95" t="n">
-        <v>7089850</v>
+        <v>7089846</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10723,10 +10723,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135265272</v>
+        <v>135265240</v>
       </c>
       <c r="B96" t="n">
-        <v>5201</v>
+        <v>8449</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10734,21 +10734,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10758,10 +10758,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>558413</v>
+        <v>558743</v>
       </c>
       <c r="R96" t="n">
-        <v>7089846</v>
+        <v>7089356</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10830,7 +10830,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135265240</v>
+        <v>135265254</v>
       </c>
       <c r="B97" t="n">
         <v>8449</v>
@@ -10865,10 +10865,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>558743</v>
+        <v>558868</v>
       </c>
       <c r="R97" t="n">
-        <v>7089356</v>
+        <v>7089444</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10910,7 +10910,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10937,45 +10937,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135265254</v>
+        <v>135265181</v>
       </c>
       <c r="B98" t="n">
-        <v>8449</v>
+        <v>99195</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>558868</v>
+        <v>558470</v>
       </c>
       <c r="R98" t="n">
-        <v>7089444</v>
+        <v>7089646</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11007,7 +11016,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11017,7 +11026,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11044,7 +11053,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135265181</v>
+        <v>135265185</v>
       </c>
       <c r="B99" t="n">
         <v>99195</v>
@@ -11074,7 +11083,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11082,16 +11091,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>558470</v>
+        <v>558454</v>
       </c>
       <c r="R99" t="n">
-        <v>7089646</v>
+        <v>7089604</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11123,7 +11137,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11133,7 +11147,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11160,7 +11174,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135265185</v>
+        <v>135265191</v>
       </c>
       <c r="B100" t="n">
         <v>99195</v>
@@ -11190,7 +11204,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11198,21 +11212,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>558454</v>
+        <v>558527</v>
       </c>
       <c r="R100" t="n">
-        <v>7089604</v>
+        <v>7089600</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11244,7 +11253,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11254,7 +11263,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11281,7 +11290,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135265191</v>
+        <v>135265194</v>
       </c>
       <c r="B101" t="n">
         <v>99195</v>
@@ -11311,7 +11320,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -11319,16 +11328,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>558527</v>
+        <v>558484</v>
       </c>
       <c r="R101" t="n">
-        <v>7089600</v>
+        <v>7089575</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11360,7 +11374,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11370,7 +11384,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11397,7 +11411,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135265194</v>
+        <v>135265217</v>
       </c>
       <c r="B102" t="n">
         <v>99195</v>
@@ -11427,7 +11441,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -11446,10 +11460,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>558484</v>
+        <v>558633</v>
       </c>
       <c r="R102" t="n">
-        <v>7089575</v>
+        <v>7089540</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11481,7 +11495,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11491,7 +11505,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11518,7 +11532,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135265217</v>
+        <v>135265232</v>
       </c>
       <c r="B103" t="n">
         <v>99195</v>
@@ -11546,31 +11560,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>558633</v>
+        <v>558660</v>
       </c>
       <c r="R103" t="n">
-        <v>7089540</v>
+        <v>7089461</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11639,7 +11639,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135265232</v>
+        <v>135265233</v>
       </c>
       <c r="B104" t="n">
         <v>99195</v>
@@ -11667,17 +11667,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>558660</v>
+        <v>558669</v>
       </c>
       <c r="R104" t="n">
-        <v>7089461</v>
+        <v>7089445</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11709,7 +11718,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11719,7 +11728,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11746,7 +11755,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135265233</v>
+        <v>135265234</v>
       </c>
       <c r="B105" t="n">
         <v>99195</v>
@@ -11776,7 +11785,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11790,10 +11799,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>558669</v>
+        <v>558670</v>
       </c>
       <c r="R105" t="n">
-        <v>7089445</v>
+        <v>7089441</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11825,7 +11834,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11835,7 +11844,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11862,7 +11871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135265234</v>
+        <v>135265235</v>
       </c>
       <c r="B106" t="n">
         <v>99195</v>
@@ -11892,7 +11901,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -11906,10 +11915,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>558670</v>
+        <v>558672</v>
       </c>
       <c r="R106" t="n">
-        <v>7089441</v>
+        <v>7089440</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11978,7 +11987,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135265235</v>
+        <v>135265237</v>
       </c>
       <c r="B107" t="n">
         <v>99195</v>
@@ -12008,7 +12017,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12022,10 +12031,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>558672</v>
+        <v>558678</v>
       </c>
       <c r="R107" t="n">
-        <v>7089440</v>
+        <v>7089413</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12057,7 +12066,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12067,7 +12076,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12094,7 +12103,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135265237</v>
+        <v>135265249</v>
       </c>
       <c r="B108" t="n">
         <v>99195</v>
@@ -12124,7 +12133,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -12138,10 +12147,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>558678</v>
+        <v>558899</v>
       </c>
       <c r="R108" t="n">
-        <v>7089413</v>
+        <v>7089389</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12173,7 +12182,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12183,7 +12192,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12210,7 +12219,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135265249</v>
+        <v>135265267</v>
       </c>
       <c r="B109" t="n">
         <v>99195</v>
@@ -12240,7 +12249,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12254,10 +12263,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>558899</v>
+        <v>558704</v>
       </c>
       <c r="R109" t="n">
-        <v>7089389</v>
+        <v>7089559</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12289,7 +12298,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12299,7 +12308,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12326,7 +12335,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135265267</v>
+        <v>135265268</v>
       </c>
       <c r="B110" t="n">
         <v>99195</v>
@@ -12356,7 +12365,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12370,10 +12379,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>558704</v>
+        <v>558728</v>
       </c>
       <c r="R110" t="n">
-        <v>7089559</v>
+        <v>7089563</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12405,7 +12414,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12415,7 +12424,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12442,7 +12451,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135265268</v>
+        <v>135265294</v>
       </c>
       <c r="B111" t="n">
         <v>99195</v>
@@ -12472,7 +12481,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -12480,16 +12489,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>558728</v>
+        <v>558486</v>
       </c>
       <c r="R111" t="n">
-        <v>7089563</v>
+        <v>7089902</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12521,7 +12535,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12531,7 +12545,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12558,7 +12572,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135265294</v>
+        <v>135265295</v>
       </c>
       <c r="B112" t="n">
         <v>99195</v>
@@ -12596,21 +12610,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>558486</v>
+        <v>558484</v>
       </c>
       <c r="R112" t="n">
-        <v>7089902</v>
+        <v>7089899</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12642,7 +12651,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12652,7 +12661,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12679,7 +12688,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135265295</v>
+        <v>135265296</v>
       </c>
       <c r="B113" t="n">
         <v>99195</v>
@@ -12709,7 +12718,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -12717,16 +12726,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>558484</v>
+        <v>558485</v>
       </c>
       <c r="R113" t="n">
-        <v>7089899</v>
+        <v>7089894</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12758,7 +12772,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12768,7 +12782,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12795,7 +12809,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135265296</v>
+        <v>135265297</v>
       </c>
       <c r="B114" t="n">
         <v>99195</v>
@@ -12825,7 +12839,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -12833,21 +12847,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>558485</v>
+        <v>558483</v>
       </c>
       <c r="R114" t="n">
-        <v>7089894</v>
+        <v>7089889</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12879,7 +12888,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12889,7 +12898,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12916,7 +12925,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135265297</v>
+        <v>135265299</v>
       </c>
       <c r="B115" t="n">
         <v>99195</v>
@@ -12946,7 +12955,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -12960,10 +12969,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>558483</v>
+        <v>558485</v>
       </c>
       <c r="R115" t="n">
-        <v>7089889</v>
+        <v>7089884</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13032,7 +13041,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135265299</v>
+        <v>135265301</v>
       </c>
       <c r="B116" t="n">
         <v>99195</v>
@@ -13060,26 +13069,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>558485</v>
+        <v>558488</v>
       </c>
       <c r="R116" t="n">
-        <v>7089884</v>
+        <v>7089880</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13148,7 +13148,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135265301</v>
+        <v>135265302</v>
       </c>
       <c r="B117" t="n">
         <v>99195</v>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>558488</v>
+        <v>558485</v>
       </c>
       <c r="R117" t="n">
-        <v>7089880</v>
+        <v>7089875</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13228,7 +13228,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13255,7 +13255,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135265302</v>
+        <v>135265305</v>
       </c>
       <c r="B118" t="n">
         <v>99195</v>
@@ -13283,17 +13283,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>558485</v>
+        <v>558475</v>
       </c>
       <c r="R118" t="n">
-        <v>7089875</v>
+        <v>7089894</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13325,7 +13334,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13335,7 +13344,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13362,7 +13371,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135265305</v>
+        <v>135265307</v>
       </c>
       <c r="B119" t="n">
         <v>99195</v>
@@ -13392,7 +13401,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -13406,10 +13415,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>558475</v>
+        <v>558481</v>
       </c>
       <c r="R119" t="n">
-        <v>7089894</v>
+        <v>7089910</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13441,7 +13450,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13451,7 +13460,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13478,7 +13487,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135265307</v>
+        <v>135265308</v>
       </c>
       <c r="B120" t="n">
         <v>99195</v>
@@ -13508,7 +13517,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -13522,10 +13531,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>558481</v>
+        <v>558478</v>
       </c>
       <c r="R120" t="n">
-        <v>7089910</v>
+        <v>7089896</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13557,7 +13566,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13567,7 +13576,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13594,7 +13603,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135265308</v>
+        <v>135265309</v>
       </c>
       <c r="B121" t="n">
         <v>99195</v>
@@ -13638,10 +13647,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>558478</v>
+        <v>558470</v>
       </c>
       <c r="R121" t="n">
-        <v>7089896</v>
+        <v>7089889</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13673,7 +13682,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13683,7 +13692,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13710,7 +13719,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135265309</v>
+        <v>135265310</v>
       </c>
       <c r="B122" t="n">
         <v>99195</v>
@@ -13738,26 +13747,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Sparvsilvberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>558470</v>
+        <v>558471</v>
       </c>
       <c r="R122" t="n">
-        <v>7089889</v>
+        <v>7089885</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13826,32 +13826,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135265310</v>
+        <v>135265190</v>
       </c>
       <c r="B123" t="n">
-        <v>99195</v>
+        <v>99217</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13861,10 +13861,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>558471</v>
+        <v>558531</v>
       </c>
       <c r="R123" t="n">
-        <v>7089885</v>
+        <v>7089614</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13933,7 +13933,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135265190</v>
+        <v>135265192</v>
       </c>
       <c r="B124" t="n">
         <v>99217</v>
@@ -13968,10 +13968,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>558531</v>
+        <v>558484</v>
       </c>
       <c r="R124" t="n">
-        <v>7089614</v>
+        <v>7089620</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14040,7 +14040,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135265192</v>
+        <v>135265195</v>
       </c>
       <c r="B125" t="n">
         <v>99217</v>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>558484</v>
+        <v>558514</v>
       </c>
       <c r="R125" t="n">
-        <v>7089620</v>
+        <v>7089556</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14147,7 +14147,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135265195</v>
+        <v>135265196</v>
       </c>
       <c r="B126" t="n">
         <v>99217</v>
@@ -14182,10 +14182,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>558514</v>
+        <v>558511</v>
       </c>
       <c r="R126" t="n">
-        <v>7089556</v>
+        <v>7089547</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14254,7 +14254,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135265196</v>
+        <v>135265199</v>
       </c>
       <c r="B127" t="n">
         <v>99217</v>
@@ -14289,10 +14289,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>558511</v>
+        <v>558541</v>
       </c>
       <c r="R127" t="n">
-        <v>7089547</v>
+        <v>7089557</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14324,7 +14324,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14361,7 +14361,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135265199</v>
+        <v>135265207</v>
       </c>
       <c r="B128" t="n">
         <v>99217</v>
@@ -14396,10 +14396,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>558541</v>
+        <v>558599</v>
       </c>
       <c r="R128" t="n">
-        <v>7089557</v>
+        <v>7089612</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14468,7 +14468,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135265207</v>
+        <v>135265210</v>
       </c>
       <c r="B129" t="n">
         <v>99217</v>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>558599</v>
+        <v>558601</v>
       </c>
       <c r="R129" t="n">
-        <v>7089612</v>
+        <v>7089578</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14575,7 +14575,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135265210</v>
+        <v>135265228</v>
       </c>
       <c r="B130" t="n">
         <v>99217</v>
@@ -14610,10 +14610,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>558601</v>
+        <v>558671</v>
       </c>
       <c r="R130" t="n">
-        <v>7089578</v>
+        <v>7089471</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14645,7 +14645,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14682,7 +14682,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135265228</v>
+        <v>135265231</v>
       </c>
       <c r="B131" t="n">
         <v>99217</v>
@@ -14717,10 +14717,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>558671</v>
+        <v>558648</v>
       </c>
       <c r="R131" t="n">
-        <v>7089471</v>
+        <v>7089470</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14789,7 +14789,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135265231</v>
+        <v>135265246</v>
       </c>
       <c r="B132" t="n">
         <v>99217</v>
@@ -14824,10 +14824,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>558648</v>
+        <v>558806</v>
       </c>
       <c r="R132" t="n">
-        <v>7089470</v>
+        <v>7089377</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14896,7 +14896,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135265246</v>
+        <v>135265291</v>
       </c>
       <c r="B133" t="n">
         <v>99217</v>
@@ -14931,10 +14931,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>558806</v>
+        <v>558480</v>
       </c>
       <c r="R133" t="n">
-        <v>7089377</v>
+        <v>7089933</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15000,113 +15000,6 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>135265291</v>
-      </c>
-      <c r="B134" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>Sparvsilvberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q134" t="n">
-        <v>558480</v>
-      </c>
-      <c r="R134" t="n">
-        <v>7089933</v>
-      </c>
-      <c r="S134" t="n">
-        <v>5</v>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>Bodum</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>17:18</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>17:18</t>
-        </is>
-      </c>
-      <c r="AD134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT134" t="inlineStr"/>
-      <c r="AW134" t="inlineStr">
-        <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AX134" t="inlineStr">
-        <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27666-2026 artfynd.xlsx
+++ b/artfynd/A 27666-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY133"/>
+  <dimension ref="A1:AZ133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265244</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265179</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265278</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362204</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265197</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265198</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265204</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265209</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265245</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265314</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362235</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362226</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2039,6 +2104,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362234</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2146,6 +2216,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265200</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265203</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2360,6 +2440,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265208</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265211</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2574,6 +2664,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265216</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2681,6 +2776,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265218</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2788,6 +2888,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265220</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2895,6 +3000,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265225</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3002,6 +3112,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265227</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3109,6 +3224,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265236</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3216,6 +3336,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265252</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3323,6 +3448,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265257</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3430,6 +3560,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265273</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3537,6 +3672,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265283</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3644,6 +3784,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265284</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3751,6 +3896,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265290</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3858,6 +4008,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265313</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3985,6 +4140,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265206</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4092,6 +4252,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265280</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4199,6 +4364,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265304</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4306,6 +4476,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265277</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4413,6 +4588,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265285</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4520,6 +4700,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265202</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4627,6 +4812,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265182</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4734,6 +4924,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265176</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4841,6 +5036,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265184</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4948,6 +5148,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265201</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5055,6 +5260,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265205</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5162,6 +5372,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265213</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5269,6 +5484,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265223</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5376,6 +5596,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265230</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5483,6 +5708,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265251</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5590,6 +5820,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265269</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5697,6 +5932,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265276</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5804,6 +6044,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265282</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5911,6 +6156,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265178</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6018,6 +6268,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265180</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6125,6 +6380,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265186</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6232,6 +6492,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265187</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6339,6 +6604,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265188</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6446,6 +6716,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265189</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6553,6 +6828,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265193</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6660,6 +6940,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265212</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6767,6 +7052,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265214</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6874,6 +7164,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265215</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6981,6 +7276,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265221</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7088,6 +7388,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265224</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7195,6 +7500,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265239</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7302,6 +7612,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265241</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7409,6 +7724,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265242</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7516,6 +7836,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265247</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7623,6 +7948,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265248</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7730,6 +8060,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265250</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7837,6 +8172,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265253</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7944,6 +8284,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265256</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8051,6 +8396,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265258</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8158,6 +8508,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265259</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8265,6 +8620,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265260</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8372,6 +8732,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265264</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8479,6 +8844,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265265</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8586,6 +8956,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265266</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8693,6 +9068,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265270</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8800,6 +9180,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265271</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8907,6 +9292,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265274</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9014,6 +9404,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265279</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9121,6 +9516,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265281</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9228,6 +9628,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265286</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9335,6 +9740,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265288</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9442,6 +9852,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265292</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9549,6 +9964,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265293</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9656,6 +10076,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265303</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9763,6 +10188,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265306</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9870,6 +10300,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265311</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9977,6 +10412,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265315</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10084,6 +10524,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265316</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10191,6 +10636,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265317</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10292,6 +10742,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362210</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10399,6 +10854,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265262</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10506,6 +10966,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265287</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10613,6 +11078,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265312</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10720,6 +11190,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265272</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10827,6 +11302,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265240</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10934,6 +11414,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265254</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11050,6 +11535,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265181</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11171,6 +11661,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265185</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11287,6 +11782,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265191</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11408,6 +11908,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265194</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11529,6 +12034,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265217</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11636,6 +12146,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265232</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11752,6 +12267,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265233</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11868,6 +12388,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265234</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11984,6 +12509,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265235</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12100,6 +12630,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265237</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12216,6 +12751,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265249</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12332,6 +12872,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265267</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12448,6 +12993,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265268</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12569,6 +13119,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265294</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12685,6 +13240,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265295</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12806,6 +13366,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265296</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12922,6 +13487,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265297</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13038,6 +13608,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265299</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13145,6 +13720,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265301</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13252,6 +13832,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265302</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13368,6 +13953,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265305</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13484,6 +14074,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265307</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13600,6 +14195,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265308</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13716,6 +14316,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265309</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13823,6 +14428,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265310</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13930,6 +14540,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265190</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14037,6 +14652,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265192</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14144,6 +14764,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265195</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14251,6 +14876,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265196</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14358,6 +14988,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265199</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14465,6 +15100,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265207</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14572,6 +15212,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265210</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14679,6 +15324,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265228</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14786,6 +15436,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265231</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14893,6 +15548,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265246</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15000,8 +15660,147 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135265291</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27666-2026 artfynd.xlsx
+++ b/artfynd/A 27666-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135265244</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135265179</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135265278</v>
       </c>
       <c r="B4" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135265197</v>
       </c>
       <c r="B6" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>135265198</v>
       </c>
       <c r="B7" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135265204</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135265209</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135265245</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>135265314</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>135265200</v>
       </c>
       <c r="B15" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135265203</v>
       </c>
       <c r="B16" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>135265208</v>
       </c>
       <c r="B17" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135265211</v>
       </c>
       <c r="B18" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135265216</v>
       </c>
       <c r="B19" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135265218</v>
       </c>
       <c r="B20" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>135265220</v>
       </c>
       <c r="B21" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>135265225</v>
       </c>
       <c r="B22" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>135265227</v>
       </c>
       <c r="B23" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135265236</v>
       </c>
       <c r="B24" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>135265252</v>
       </c>
       <c r="B25" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>135265257</v>
       </c>
       <c r="B26" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>135265273</v>
       </c>
       <c r="B27" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>135265283</v>
       </c>
       <c r="B28" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135265284</v>
       </c>
       <c r="B29" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>135265290</v>
       </c>
       <c r="B30" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>135265313</v>
       </c>
       <c r="B31" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>135265206</v>
       </c>
       <c r="B32" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>135265280</v>
       </c>
       <c r="B33" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>135265304</v>
       </c>
       <c r="B34" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>135265277</v>
       </c>
       <c r="B35" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>135265285</v>
       </c>
       <c r="B36" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>135265202</v>
       </c>
       <c r="B37" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>135265182</v>
       </c>
       <c r="B38" t="n">
-        <v>96037</v>
+        <v>96081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>135265176</v>
       </c>
       <c r="B39" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>135265184</v>
       </c>
       <c r="B40" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>135265201</v>
       </c>
       <c r="B41" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>135265205</v>
       </c>
       <c r="B42" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>135265213</v>
       </c>
       <c r="B43" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>135265223</v>
       </c>
       <c r="B44" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>135265230</v>
       </c>
       <c r="B45" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>135265251</v>
       </c>
       <c r="B46" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>135265269</v>
       </c>
       <c r="B47" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>135265276</v>
       </c>
       <c r="B48" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>135265282</v>
       </c>
       <c r="B49" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>135265178</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>135265180</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>135265186</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>135265187</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>135265188</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>135265189</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>135265193</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>135265212</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>135265214</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>135265215</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>135265221</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>135265224</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>135265239</v>
       </c>
       <c r="B62" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>135265241</v>
       </c>
       <c r="B63" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>135265242</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>135265247</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>135265248</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>135265250</v>
       </c>
       <c r="B67" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>135265253</v>
       </c>
       <c r="B68" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>135265256</v>
       </c>
       <c r="B69" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>135265258</v>
       </c>
       <c r="B70" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>135265259</v>
       </c>
       <c r="B71" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>135265260</v>
       </c>
       <c r="B72" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135265264</v>
       </c>
       <c r="B73" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135265265</v>
       </c>
       <c r="B74" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>135265266</v>
       </c>
       <c r="B75" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>135265270</v>
       </c>
       <c r="B76" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>135265271</v>
       </c>
       <c r="B77" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>135265274</v>
       </c>
       <c r="B78" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>135265279</v>
       </c>
       <c r="B79" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>135265281</v>
       </c>
       <c r="B80" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>135265286</v>
       </c>
       <c r="B81" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>135265288</v>
       </c>
       <c r="B82" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>135265292</v>
       </c>
       <c r="B83" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135265293</v>
       </c>
       <c r="B84" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>135265303</v>
       </c>
       <c r="B85" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>135265306</v>
       </c>
       <c r="B86" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>135265311</v>
       </c>
       <c r="B87" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>135265315</v>
       </c>
       <c r="B88" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>135265316</v>
       </c>
       <c r="B89" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>135265317</v>
       </c>
       <c r="B90" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>135265262</v>
       </c>
       <c r="B92" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>135265240</v>
       </c>
       <c r="B96" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>135265254</v>
       </c>
       <c r="B97" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>135265181</v>
       </c>
       <c r="B98" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>135265185</v>
       </c>
       <c r="B99" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>135265191</v>
       </c>
       <c r="B100" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>135265194</v>
       </c>
       <c r="B101" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>135265217</v>
       </c>
       <c r="B102" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>135265232</v>
       </c>
       <c r="B103" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>135265233</v>
       </c>
       <c r="B104" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>135265234</v>
       </c>
       <c r="B105" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>135265235</v>
       </c>
       <c r="B106" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>135265237</v>
       </c>
       <c r="B107" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>135265249</v>
       </c>
       <c r="B108" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>135265267</v>
       </c>
       <c r="B109" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135265268</v>
       </c>
       <c r="B110" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>135265294</v>
       </c>
       <c r="B111" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>135265295</v>
       </c>
       <c r="B112" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>135265296</v>
       </c>
       <c r="B113" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>135265297</v>
       </c>
       <c r="B114" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>135265299</v>
       </c>
       <c r="B115" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>135265301</v>
       </c>
       <c r="B116" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>135265302</v>
       </c>
       <c r="B117" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>135265305</v>
       </c>
       <c r="B118" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>135265307</v>
       </c>
       <c r="B119" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>135265308</v>
       </c>
       <c r="B120" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>135265309</v>
       </c>
       <c r="B121" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>135265310</v>
       </c>
       <c r="B122" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>135265190</v>
       </c>
       <c r="B123" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>135265192</v>
       </c>
       <c r="B124" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>135265195</v>
       </c>
       <c r="B125" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>135265196</v>
       </c>
       <c r="B126" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>135265199</v>
       </c>
       <c r="B127" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>135265207</v>
       </c>
       <c r="B128" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>135265210</v>
       </c>
       <c r="B129" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>135265228</v>
       </c>
       <c r="B130" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>135265231</v>
       </c>
       <c r="B131" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>135265246</v>
       </c>
       <c r="B132" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>135265291</v>
       </c>
       <c r="B133" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 27666-2026 artfynd.xlsx
+++ b/artfynd/A 27666-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135265244</v>
       </c>
       <c r="B2" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135265179</v>
       </c>
       <c r="B3" t="n">
-        <v>83383</v>
+        <v>83410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135265278</v>
       </c>
       <c r="B4" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135265197</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>135265198</v>
       </c>
       <c r="B7" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135265204</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135265209</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135265245</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>135265314</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>135265200</v>
       </c>
       <c r="B15" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135265203</v>
       </c>
       <c r="B16" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>135265208</v>
       </c>
       <c r="B17" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135265211</v>
       </c>
       <c r="B18" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135265216</v>
       </c>
       <c r="B19" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135265218</v>
       </c>
       <c r="B20" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>135265220</v>
       </c>
       <c r="B21" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>135265225</v>
       </c>
       <c r="B22" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>135265227</v>
       </c>
       <c r="B23" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135265236</v>
       </c>
       <c r="B24" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>135265252</v>
       </c>
       <c r="B25" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>135265257</v>
       </c>
       <c r="B26" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>135265273</v>
       </c>
       <c r="B27" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>135265283</v>
       </c>
       <c r="B28" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135265284</v>
       </c>
       <c r="B29" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>135265290</v>
       </c>
       <c r="B30" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>135265313</v>
       </c>
       <c r="B31" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>135265206</v>
       </c>
       <c r="B32" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>135265280</v>
       </c>
       <c r="B33" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>135265304</v>
       </c>
       <c r="B34" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>135265277</v>
       </c>
       <c r="B35" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>135265285</v>
       </c>
       <c r="B36" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>135265202</v>
       </c>
       <c r="B37" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>135265182</v>
       </c>
       <c r="B38" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>135265176</v>
       </c>
       <c r="B39" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>135265184</v>
       </c>
       <c r="B40" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>135265201</v>
       </c>
       <c r="B41" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>135265205</v>
       </c>
       <c r="B42" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>135265213</v>
       </c>
       <c r="B43" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>135265223</v>
       </c>
       <c r="B44" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>135265230</v>
       </c>
       <c r="B45" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>135265251</v>
       </c>
       <c r="B46" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>135265269</v>
       </c>
       <c r="B47" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>135265276</v>
       </c>
       <c r="B48" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>135265282</v>
       </c>
       <c r="B49" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>135265178</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>135265180</v>
       </c>
       <c r="B51" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>135265186</v>
       </c>
       <c r="B52" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>135265187</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>135265188</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>135265189</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>135265193</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>135265212</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>135265214</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>135265215</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>135265221</v>
       </c>
       <c r="B60" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>135265224</v>
       </c>
       <c r="B61" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>135265239</v>
       </c>
       <c r="B62" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>135265241</v>
       </c>
       <c r="B63" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>135265242</v>
       </c>
       <c r="B64" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>135265247</v>
       </c>
       <c r="B65" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>135265248</v>
       </c>
       <c r="B66" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>135265250</v>
       </c>
       <c r="B67" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>135265253</v>
       </c>
       <c r="B68" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>135265256</v>
       </c>
       <c r="B69" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>135265258</v>
       </c>
       <c r="B70" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>135265259</v>
       </c>
       <c r="B71" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>135265260</v>
       </c>
       <c r="B72" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>135265264</v>
       </c>
       <c r="B73" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135265265</v>
       </c>
       <c r="B74" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>135265266</v>
       </c>
       <c r="B75" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>135265270</v>
       </c>
       <c r="B76" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>135265271</v>
       </c>
       <c r="B77" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>135265274</v>
       </c>
       <c r="B78" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>135265279</v>
       </c>
       <c r="B79" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>135265281</v>
       </c>
       <c r="B80" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>135265286</v>
       </c>
       <c r="B81" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>135265288</v>
       </c>
       <c r="B82" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>135265292</v>
       </c>
       <c r="B83" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135265293</v>
       </c>
       <c r="B84" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>135265303</v>
       </c>
       <c r="B85" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>135265306</v>
       </c>
       <c r="B86" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>135265311</v>
       </c>
       <c r="B87" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>135265315</v>
       </c>
       <c r="B88" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>135265316</v>
       </c>
       <c r="B89" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>135265317</v>
       </c>
       <c r="B90" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>135265262</v>
       </c>
       <c r="B92" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>135265181</v>
       </c>
       <c r="B98" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>135265185</v>
       </c>
       <c r="B99" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>135265191</v>
       </c>
       <c r="B100" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>135265194</v>
       </c>
       <c r="B101" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>135265217</v>
       </c>
       <c r="B102" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>135265232</v>
       </c>
       <c r="B103" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>135265233</v>
       </c>
       <c r="B104" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>135265234</v>
       </c>
       <c r="B105" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>135265235</v>
       </c>
       <c r="B106" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>135265237</v>
       </c>
       <c r="B107" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>135265249</v>
       </c>
       <c r="B108" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>135265267</v>
       </c>
       <c r="B109" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135265268</v>
       </c>
       <c r="B110" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>135265294</v>
       </c>
       <c r="B111" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>135265295</v>
       </c>
       <c r="B112" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>135265296</v>
       </c>
       <c r="B113" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>135265297</v>
       </c>
       <c r="B114" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>135265299</v>
       </c>
       <c r="B115" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>135265301</v>
       </c>
       <c r="B116" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>135265302</v>
       </c>
       <c r="B117" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>135265305</v>
       </c>
       <c r="B118" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>135265307</v>
       </c>
       <c r="B119" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>135265308</v>
       </c>
       <c r="B120" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>135265309</v>
       </c>
       <c r="B121" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>135265310</v>
       </c>
       <c r="B122" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>135265190</v>
       </c>
       <c r="B123" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>135265192</v>
       </c>
       <c r="B124" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>135265195</v>
       </c>
       <c r="B125" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>135265196</v>
       </c>
       <c r="B126" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>135265199</v>
       </c>
       <c r="B127" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>135265207</v>
       </c>
       <c r="B128" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>135265210</v>
       </c>
       <c r="B129" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>135265228</v>
       </c>
       <c r="B130" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>135265231</v>
       </c>
       <c r="B131" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>135265246</v>
       </c>
       <c r="B132" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>135265291</v>
       </c>
       <c r="B133" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 27666-2026 artfynd.xlsx
+++ b/artfynd/A 27666-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135265244</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>135265197</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>135265198</v>
       </c>
       <c r="B7" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135265204</v>
       </c>
       <c r="B8" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>135265209</v>
       </c>
       <c r="B9" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>135265245</v>
       </c>
       <c r="B10" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>135265314</v>
       </c>
       <c r="B11" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>135265200</v>
       </c>
       <c r="B15" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>135265203</v>
       </c>
       <c r="B16" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>135265208</v>
       </c>
       <c r="B17" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135265211</v>
       </c>
       <c r="B18" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>135265216</v>
       </c>
       <c r="B19" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135265218</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>135265220</v>
       </c>
       <c r="B21" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>135265225</v>
       </c>
       <c r="B22" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>135265227</v>
       </c>
       <c r="B23" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135265236</v>
       </c>
       <c r="B24" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>135265252</v>
       </c>
       <c r="B25" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>135265257</v>
       </c>
       <c r="B26" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>135265273</v>
       </c>
       <c r="B27" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>135265283</v>
       </c>
       <c r="B28" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135265284</v>
       </c>
       <c r="B29" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>135265290</v>
       </c>
       <c r="B30" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>135265313</v>
       </c>
       <c r="B31" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>135265206</v>
       </c>
       <c r="B32" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>135265280</v>
       </c>
       <c r="B33" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>135265304</v>
       </c>
       <c r="B34" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>135265277</v>
       </c>
       <c r="B35" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>135265285</v>
       </c>
       <c r="B36" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>135265202</v>
       </c>
       <c r="B37" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>135265182</v>
       </c>
       <c r="B38" t="n">
-        <v>96113</v>
+        <v>96115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>135265176</v>
       </c>
       <c r="B39" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>135265184</v>
       </c>
       <c r="B40" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>135265201</v>
       </c>
       <c r="B41" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>135265205</v>
       </c>
       <c r="B42" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>135265213</v>
       </c>
       <c r="B43" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>135265223</v>
       </c>
       <c r="B44" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>135265230</v>
       </c>
       <c r="B45" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>135265251</v>
       </c>
       <c r="B46" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>135265269</v>
       </c>
       <c r="B47" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>135265276</v>
       </c>
       <c r="B48" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>135265282</v>
       </c>
       <c r="B49" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>135265181</v>
       </c>
       <c r="B98" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>135265185</v>
       </c>
       <c r="B99" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>135265191</v>
       </c>
       <c r="B100" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>135265194</v>
       </c>
       <c r="B101" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>135265217</v>
       </c>
       <c r="B102" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>135265232</v>
       </c>
       <c r="B103" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>135265233</v>
       </c>
       <c r="B104" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>135265234</v>
       </c>
       <c r="B105" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>135265235</v>
       </c>
       <c r="B106" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>135265237</v>
       </c>
       <c r="B107" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>135265249</v>
       </c>
       <c r="B108" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>135265267</v>
       </c>
       <c r="B109" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>135265268</v>
       </c>
       <c r="B110" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>135265294</v>
       </c>
       <c r="B111" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>135265295</v>
       </c>
       <c r="B112" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>135265296</v>
       </c>
       <c r="B113" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>135265297</v>
       </c>
       <c r="B114" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>135265299</v>
       </c>
       <c r="B115" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>135265301</v>
       </c>
       <c r="B116" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>135265302</v>
       </c>
       <c r="B117" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>135265305</v>
       </c>
       <c r="B118" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>135265307</v>
       </c>
       <c r="B119" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>135265308</v>
       </c>
       <c r="B120" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>135265309</v>
       </c>
       <c r="B121" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>135265310</v>
       </c>
       <c r="B122" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>135265190</v>
       </c>
       <c r="B123" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>135265192</v>
       </c>
       <c r="B124" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>135265195</v>
       </c>
       <c r="B125" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>135265196</v>
       </c>
       <c r="B126" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>135265199</v>
       </c>
       <c r="B127" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>135265207</v>
       </c>
       <c r="B128" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>135265210</v>
       </c>
       <c r="B129" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>135265228</v>
       </c>
       <c r="B130" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>135265231</v>
       </c>
       <c r="B131" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>135265246</v>
       </c>
       <c r="B132" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>135265291</v>
       </c>
       <c r="B133" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
